--- a/injuries.xlsx
+++ b/injuries.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Injuries" sheetId="1" r:id="Rea5309a651e84048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Injuries" sheetId="1" r:id="R4d3bb909a2cf4fb2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,12 +21,13 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF35FF98"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF111111"/>
+      <x:color rgb="FFDC2626"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -39,7 +40,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0B2016"/>
+        <x:fgColor rgb="FF111827"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -50,7 +51,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -69,15 +70,35 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InjuryOutTable" displayName="InjuryOutTable" ref="A1:D21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="Player"/>
+    <x:tableColumn id="2" name="Team"/>
+    <x:tableColumn id="3" name="Status"/>
+    <x:tableColumn id="4" name="Est. Time"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -275,8 +296,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -284,135 +307,299 @@
         <x:v>Player</x:v>
       </x:c>
       <x:c r="B1" s="5" t="str">
+        <x:v>Team</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
         <x:v>Status</x:v>
       </x:c>
+      <x:c r="D1" s="5" t="str">
+        <x:v>Est. Time</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11" t="str">
+      <x:c r="A2" s="10" t="str">
+        <x:v>Mathis Dousou Yovo</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>Asvel</x:v>
+      </x:c>
+      <x:c r="C2" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>-</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="10" t="str">
+        <x:v>Gur Lavy</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>Maccabi</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>Nikola Djurisic</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>Zvezda</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="10" t="str">
+        <x:v>Garrison Mathews</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>Milano</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>~</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>DeQuan Jeffries</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Besiktas</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>~7 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
+        <x:v>Nigel Williams Goss</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>Zalgiris</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>2 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
         <x:v>Kevin Kokila</x:v>
       </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="11" t="str">
+      <x:c r="B8" s="10" t="str">
+        <x:v>Virtus</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>~2 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
         <x:v>Vanja Marinkovic</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="11" t="str">
+      <x:c r="B9" s="10" t="str">
+        <x:v>Partizan</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>~</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>Derek Willis</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Partizan</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>~3 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
         <x:v>Usman Garuba</x:v>
       </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="B11" s="10" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>long term</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
         <x:v>Georgios Papagiannis</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="B12" s="10" t="str">
+        <x:v>Efes</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>long term</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
         <x:v>Tamir Blatt</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="B13" s="10" t="str">
+        <x:v>Hapoel</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>Tomer Ginat</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Hapoel</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
         <x:v>Tyler Ennis</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="B15" s="10" t="str">
+        <x:v>Hapoel</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>long term</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>Josh Nebo</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>Barça</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>2-3 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
         <x:v>Yoan Makoundou</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="str">
+      <x:c r="B17" s="10" t="str">
+        <x:v>Barça</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>5 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
         <x:v>Moustapha Fall</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="str">
+      <x:c r="B18" s="10" t="str">
+        <x:v>Pao</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>~1 week</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
         <x:v>Kendrick Nunn</x:v>
       </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>Nigel Hayes-Davis</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="str">
+      <x:c r="B19" s="10" t="str">
+        <x:v>Pao</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>~1 week</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
+        <x:v>Nigel Hayes Davis</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>Pao</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>~3 weeks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
         <x:v>Kostas Sloukas</x:v>
       </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>Josh Nebo</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="str">
-        <x:v>Kamar Baldwin</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="11" t="str">
-        <x:v>Garrison Mathews</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="str">
-        <x:v>OUT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="11" t="str">
-        <x:v>Amir Coffey</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="str">
-        <x:v>OUT</x:v>
+      <x:c r="B21" s="10" t="str">
+        <x:v>Pao</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>OUT</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>~</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="B2:B200">
-      <x:formula1>"OUT,GTD,Doubt"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5e5731dbd104b4e"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
--- a/injuries.xlsx
+++ b/injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yhbrm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2B79AB-E7B3-403C-BE3A-A7062DC34350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2317DB5F-E629-4F88-81F9-AE99431DC348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>Player</t>
   </si>
@@ -68,9 +68,6 @@
     <t>unknown</t>
   </si>
   <si>
-    <t>Nikola Djurisic</t>
-  </si>
-  <si>
     <t>Zvezda</t>
   </si>
   <si>
@@ -95,15 +92,6 @@
     <t>2 weeks</t>
   </si>
   <si>
-    <t>Kevin Kokila</t>
-  </si>
-  <si>
-    <t>Virtus</t>
-  </si>
-  <si>
-    <t>~2 weeks</t>
-  </si>
-  <si>
     <t>Vanja Marinkovic</t>
   </si>
   <si>
@@ -143,24 +131,15 @@
     <t>Tyler Ennis</t>
   </si>
   <si>
-    <t>Josh Nebo</t>
-  </si>
-  <si>
     <t>Barça</t>
   </si>
   <si>
-    <t>2-3 weeks</t>
-  </si>
-  <si>
     <t>Yoan Makoundou</t>
   </si>
   <si>
     <t>5 weeks</t>
   </si>
   <si>
-    <t>Moustapha Fall</t>
-  </si>
-  <si>
     <t>Pao</t>
   </si>
   <si>
@@ -171,6 +150,12 @@
   </si>
   <si>
     <t>Kostas Sloukas</t>
+  </si>
+  <si>
+    <t>Johnathan Motley</t>
+  </si>
+  <si>
+    <t>Mike James</t>
   </si>
 </sst>
 </file>
@@ -249,7 +234,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InjuryOutTable" displayName="InjuryOutTable" ref="A1:D19" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InjuryOutTable" displayName="InjuryOutTable" ref="A1:D17" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Player"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Team"/>
@@ -455,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -508,52 +493,52 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
@@ -573,57 +558,57 @@
         <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>6</v>
@@ -634,100 +619,72 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
